--- a/Presupuestos.xlsx
+++ b/Presupuestos.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF975887-D610-4005-8DEA-00319CC6C64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F97C51-2492-4AD6-BB2B-737CC9E347CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9481DF28-0B3E-48A4-9B25-BB3654989BFF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9481DF28-0B3E-48A4-9B25-BB3654989BFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$P$18</definedName>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="41">
   <si>
     <t>EQUIPO</t>
   </si>
@@ -147,13 +148,31 @@
   </si>
   <si>
     <t>CUARTOS</t>
+  </si>
+  <si>
+    <t>Atletico de Madrid</t>
+  </si>
+  <si>
+    <t>Casa Pia AC</t>
+  </si>
+  <si>
+    <t>Urawa Red Diamonds</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Club America</t>
+  </si>
+  <si>
+    <t>DINERO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,8 +188,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -204,6 +231,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -272,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -280,6 +313,24 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -298,22 +349,13 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -678,23 +720,23 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3" t="s">
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="6" t="s">
+      <c r="G1" s="10"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="7"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="13" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -703,10 +745,10 @@
       <c r="N1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -714,69 +756,69 @@
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="13"/>
+      <c r="L2" s="6"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="14"/>
+      <c r="P2" s="7"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="2">
         <v>320</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="2">
         <v>105</v>
       </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="11" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="4">
         <v>320</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="13">
+      <c r="H3" s="4"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6">
         <v>20</v>
       </c>
       <c r="M3" s="1">
@@ -787,7 +829,7 @@
         <v>765</v>
       </c>
       <c r="O3" s="1"/>
-      <c r="P3" s="14">
+      <c r="P3" s="7">
         <f t="shared" ref="P3:P11" si="0">M3+N3-O3</f>
         <v>2497</v>
       </c>
@@ -796,33 +838,33 @@
       <c r="A4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="2">
         <v>300</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="2">
         <v>95</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="2">
         <v>140</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="4">
         <v>170</v>
       </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="12" t="s">
+      <c r="H4" s="4"/>
+      <c r="I4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="5">
         <v>200</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="13">
+      <c r="K4" s="5"/>
+      <c r="L4" s="6">
         <v>10</v>
       </c>
       <c r="M4" s="1">
@@ -833,7 +875,7 @@
         <v>915</v>
       </c>
       <c r="O4" s="1"/>
-      <c r="P4" s="14">
+      <c r="P4" s="7">
         <f t="shared" si="0"/>
         <v>1021</v>
       </c>
@@ -842,31 +884,31 @@
       <c r="A5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="2">
         <v>3</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="2">
         <v>280</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="2">
         <v>50</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="11" t="s">
+      <c r="E5" s="2"/>
+      <c r="F5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="4">
         <v>100</v>
       </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="12" t="s">
+      <c r="H5" s="4"/>
+      <c r="I5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="5">
         <v>250</v>
       </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="13">
+      <c r="K5" s="5"/>
+      <c r="L5" s="6">
         <v>10</v>
       </c>
       <c r="M5" s="1">
@@ -877,7 +919,7 @@
         <v>690</v>
       </c>
       <c r="O5" s="1"/>
-      <c r="P5" s="14">
+      <c r="P5" s="7">
         <f t="shared" si="0"/>
         <v>1123</v>
       </c>
@@ -886,31 +928,31 @@
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="2">
         <v>4</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="2">
         <v>260</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="2">
         <v>27</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="11" t="s">
+      <c r="E6" s="2"/>
+      <c r="F6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="4">
         <v>200</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="4">
         <v>60</v>
       </c>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12">
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5">
         <v>100</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="6">
         <v>20</v>
       </c>
       <c r="M6" s="1">
@@ -921,7 +963,7 @@
         <v>667</v>
       </c>
       <c r="O6" s="1"/>
-      <c r="P6" s="14">
+      <c r="P6" s="7">
         <f t="shared" si="0"/>
         <v>1932</v>
       </c>
@@ -930,28 +972,28 @@
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="2">
         <v>5</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="2">
         <v>240</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="13"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="6"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1">
         <f t="shared" si="1"/>
         <v>240</v>
       </c>
       <c r="O7" s="1"/>
-      <c r="P7" s="14">
+      <c r="P7" s="7">
         <f t="shared" si="0"/>
         <v>240</v>
       </c>
@@ -960,31 +1002,31 @@
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="2">
         <v>6</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="2">
         <v>220</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10">
+      <c r="D8" s="2"/>
+      <c r="E8" s="2">
         <v>65</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="4">
         <v>170</v>
       </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="12" t="s">
+      <c r="H8" s="4"/>
+      <c r="I8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="5">
         <v>250</v>
       </c>
-      <c r="K8" s="12"/>
-      <c r="L8" s="13">
+      <c r="K8" s="5"/>
+      <c r="L8" s="6">
         <v>20</v>
       </c>
       <c r="M8" s="1">
@@ -995,7 +1037,7 @@
         <v>725</v>
       </c>
       <c r="O8" s="1"/>
-      <c r="P8" s="14">
+      <c r="P8" s="7">
         <f t="shared" si="0"/>
         <v>2822</v>
       </c>
@@ -1004,25 +1046,25 @@
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="2">
         <v>7</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="2">
         <v>200</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="11" t="s">
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="4">
         <v>100</v>
       </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="13">
+      <c r="H9" s="4"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="6">
         <v>20</v>
       </c>
       <c r="M9" s="1">
@@ -1033,7 +1075,7 @@
         <v>320</v>
       </c>
       <c r="O9" s="1"/>
-      <c r="P9" s="14">
+      <c r="P9" s="7">
         <f t="shared" si="0"/>
         <v>525</v>
       </c>
@@ -1042,29 +1084,29 @@
       <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="2">
         <v>8</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="2">
         <v>180</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="2">
         <v>105</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="2">
         <v>50</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="12" t="s">
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="5">
         <v>200</v>
       </c>
-      <c r="K10" s="12"/>
-      <c r="L10" s="13"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="6"/>
       <c r="M10" s="1">
         <v>251</v>
       </c>
@@ -1073,7 +1115,7 @@
         <v>535</v>
       </c>
       <c r="O10" s="1"/>
-      <c r="P10" s="14">
+      <c r="P10" s="7">
         <f t="shared" si="0"/>
         <v>786</v>
       </c>
@@ -1082,25 +1124,25 @@
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="2">
         <v>9</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="2">
         <v>160</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="12" t="s">
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="5">
         <v>200</v>
       </c>
-      <c r="K11" s="12"/>
-      <c r="L11" s="13"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="6"/>
       <c r="M11" s="1">
         <v>1259</v>
       </c>
@@ -1109,7 +1151,7 @@
         <v>360</v>
       </c>
       <c r="O11" s="1"/>
-      <c r="P11" s="14">
+      <c r="P11" s="7">
         <f t="shared" si="0"/>
         <v>1619</v>
       </c>
@@ -1118,21 +1160,21 @@
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="2">
         <v>10</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="2">
         <v>140</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="13">
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="6">
         <v>10</v>
       </c>
       <c r="M12" s="1">
@@ -1145,7 +1187,7 @@
       <c r="O12" s="1">
         <v>158</v>
       </c>
-      <c r="P12" s="14">
+      <c r="P12" s="7">
         <f>M12+N12-O12</f>
         <v>913</v>
       </c>
@@ -1154,25 +1196,25 @@
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="2">
         <v>11</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="2">
         <v>120</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="11" t="s">
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="4">
         <v>100</v>
       </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="13">
+      <c r="H13" s="4"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="6">
         <v>20</v>
       </c>
       <c r="M13" s="1">
@@ -1183,7 +1225,7 @@
         <v>240</v>
       </c>
       <c r="O13" s="1"/>
-      <c r="P13" s="14">
+      <c r="P13" s="7">
         <f t="shared" ref="P13:P18" si="2">M13+N13-O13</f>
         <v>540</v>
       </c>
@@ -1192,23 +1234,23 @@
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="2">
         <v>12</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="2">
         <v>100</v>
       </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10">
+      <c r="D14" s="2"/>
+      <c r="E14" s="2">
         <v>45</v>
       </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="13">
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="6">
         <v>10</v>
       </c>
       <c r="M14" s="1">
@@ -1219,7 +1261,7 @@
         <v>155</v>
       </c>
       <c r="O14" s="1"/>
-      <c r="P14" s="14">
+      <c r="P14" s="7">
         <f t="shared" si="2"/>
         <v>346</v>
       </c>
@@ -1228,26 +1270,26 @@
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="2">
         <v>13</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="13"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="6"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O15" s="1"/>
-      <c r="P15" s="14">
+      <c r="P15" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1256,26 +1298,26 @@
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="2">
         <v>14</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="13"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="6"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O16" s="1"/>
-      <c r="P16" s="14">
+      <c r="P16" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1284,30 +1326,30 @@
       <c r="A17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="2">
         <v>15</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="12" t="s">
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="5">
         <v>200</v>
       </c>
-      <c r="K17" s="12"/>
-      <c r="L17" s="13"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="6"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
       <c r="O17" s="1"/>
-      <c r="P17" s="14">
+      <c r="P17" s="7">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
@@ -1316,26 +1358,26 @@
       <c r="A18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="2">
         <v>16</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="13"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="6"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O18" s="1"/>
-      <c r="P18" s="14">
+      <c r="P18" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1357,4 +1399,170 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F198FC4B-51A6-43F8-996F-53C097AA9FD1}">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" style="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="16">
+        <v>2675</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="16">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="16">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="16">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="16">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="16">
+        <v>2569</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="16">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="16">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="16">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="16">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="16">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="16">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="16">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="16">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="16">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="16">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="16">
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Presupuestos.xlsx
+++ b/Presupuestos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F97C51-2492-4AD6-BB2B-737CC9E347CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC6B31C-D1C5-43B0-8F78-914ADFA43CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9481DF28-0B3E-48A4-9B25-BB3654989BFF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{9481DF28-0B3E-48A4-9B25-BB3654989BFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
   <si>
     <t>EQUIPO</t>
   </si>
@@ -166,6 +166,27 @@
   </si>
   <si>
     <t>DINERO</t>
+  </si>
+  <si>
+    <t>COMPRAS</t>
+  </si>
+  <si>
+    <t>VENTAS</t>
+  </si>
+  <si>
+    <t>LIBRES</t>
+  </si>
+  <si>
+    <t>PRESTAMOS</t>
+  </si>
+  <si>
+    <t>Arnold 2 temporadas</t>
+  </si>
+  <si>
+    <t>BAJAS</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
@@ -305,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -328,6 +349,15 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -349,14 +379,8 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -720,22 +744,22 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="9" t="s">
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="12" t="s">
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="13"/>
-      <c r="K1" s="14"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="17"/>
       <c r="L1" s="6" t="s">
         <v>6</v>
       </c>
@@ -1403,162 +1427,198 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F198FC4B-51A6-43F8-996F-53C097AA9FD1}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" style="8" customWidth="1"/>
+    <col min="3" max="5" width="11.5546875" style="8"/>
+    <col min="6" max="6" width="19" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="9" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="C1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="9">
         <v>2675</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="9">
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="9">
         <v>1000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="9">
         <v>2152</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="9">
         <v>164</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="9">
         <v>2569</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="9">
         <v>194</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="9">
         <v>440</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="9">
         <v>1920</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="9">
         <v>759</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="9">
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="9">
         <v>223</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="9">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="9">
         <v>280</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="9">
         <v>300</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="17" t="s">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="9">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="9">
         <v>300</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="17" t="s">
+      <c r="C18" s="8">
+        <v>75</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18">
+        <v>88</v>
+      </c>
+      <c r="H18">
+        <f>B18-C18+D18-E18-G18</f>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="9">
         <v>300</v>
       </c>
     </row>

--- a/Presupuestos.xlsx
+++ b/Presupuestos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC6B31C-D1C5-43B0-8F78-914ADFA43CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9378B7-7D6B-4108-B579-078BC470C962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{9481DF28-0B3E-48A4-9B25-BB3654989BFF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9481DF28-0B3E-48A4-9B25-BB3654989BFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
   <si>
     <t>EQUIPO</t>
   </si>
@@ -187,13 +187,22 @@
   </si>
   <si>
     <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Julian x Dembele 2 temp</t>
+  </si>
+  <si>
+    <t>Ousmane Dembélé x Julián Alvarez -&gt; Inter de Milan 2 temp Lionel Messi x  -&gt; AC Milan 1 temp</t>
+  </si>
+  <si>
+    <t>eliot anderson -&gt; como x 50 M 1 temp</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,14 +214,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -257,7 +258,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF002060"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -326,7 +327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -352,11 +353,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -379,8 +377,14 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -744,22 +748,22 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="12" t="s">
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="13"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="15" t="s">
+      <c r="G1" s="12"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="16"/>
-      <c r="K1" s="17"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="16"/>
       <c r="L1" s="6" t="s">
         <v>6</v>
       </c>
@@ -1433,7 +1437,7 @@
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.33203125" style="8" customWidth="1"/>
     <col min="3" max="5" width="11.5546875" style="8"/>
-    <col min="6" max="6" width="19" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="49.44140625" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -1443,183 +1447,387 @@
       <c r="B1" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="9" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="18">
         <v>2675</v>
       </c>
+      <c r="C2" s="18">
+        <v>50</v>
+      </c>
+      <c r="D2" s="18">
+        <v>20</v>
+      </c>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="18">
+        <v>70</v>
+      </c>
+      <c r="H2" s="18">
+        <f>B2-C2+D2-E2-G2</f>
+        <v>2575</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B3" s="9">
         <v>300</v>
       </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9">
+        <v>119</v>
+      </c>
+      <c r="H3" s="9">
+        <f t="shared" ref="H3:H19" si="0">B3-C3+D3-E3-G3</f>
+        <v>181</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="18">
         <v>1000</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="C4" s="18">
+        <v>80</v>
+      </c>
+      <c r="D4" s="18">
+        <v>140</v>
+      </c>
+      <c r="E4" s="18">
+        <v>250</v>
+      </c>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18">
+        <f t="shared" si="0"/>
+        <v>810</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="18">
         <v>2152</v>
       </c>
+      <c r="C5" s="18">
+        <v>60</v>
+      </c>
+      <c r="D5" s="18">
+        <v>95</v>
+      </c>
+      <c r="E5" s="18"/>
+      <c r="F5" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="18">
+        <v>33</v>
+      </c>
+      <c r="H5" s="18">
+        <f t="shared" si="0"/>
+        <v>2154</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="18">
         <v>164</v>
       </c>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18">
+        <v>50</v>
+      </c>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18">
+        <v>3</v>
+      </c>
+      <c r="H6" s="18">
+        <f t="shared" si="0"/>
+        <v>211</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="18">
         <v>2569</v>
       </c>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18">
+        <f t="shared" si="0"/>
+        <v>2569</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="18">
         <v>194</v>
       </c>
+      <c r="C8" s="18">
+        <v>60</v>
+      </c>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18">
+        <v>15</v>
+      </c>
+      <c r="H8" s="18">
+        <f t="shared" si="0"/>
+        <v>119</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="18">
         <v>440</v>
       </c>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="18">
         <v>1920</v>
       </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18">
+        <v>215</v>
+      </c>
+      <c r="E10" s="18">
+        <v>0</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="18">
+        <v>14</v>
+      </c>
+      <c r="H10" s="18">
+        <f t="shared" si="0"/>
+        <v>2121</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="18">
         <v>759</v>
       </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18">
+        <f t="shared" si="0"/>
+        <v>759</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="18">
         <v>300</v>
       </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="18">
         <v>223</v>
       </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18">
+        <f t="shared" si="0"/>
+        <v>223</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="18">
         <v>12</v>
       </c>
+      <c r="C14" s="18">
+        <v>45</v>
+      </c>
+      <c r="D14" s="18">
+        <v>40</v>
+      </c>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18">
+        <v>18</v>
+      </c>
+      <c r="H14" s="18">
+        <f t="shared" si="0"/>
+        <v>-11</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="18">
         <v>280</v>
       </c>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18">
+        <f t="shared" si="0"/>
+        <v>280</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B16" s="9">
         <v>300</v>
       </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="9">
         <v>300</v>
       </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="18">
         <v>300</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="18">
         <v>75</v>
       </c>
-      <c r="E18" s="8">
+      <c r="D18" s="18"/>
+      <c r="E18" s="18">
         <v>0</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="18">
         <v>88</v>
       </c>
-      <c r="H18">
-        <f>B18-C18+D18-E18-G18</f>
+      <c r="H18" s="18">
+        <f t="shared" si="0"/>
         <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="18">
         <v>300</v>
+      </c>
+      <c r="C19" s="18">
+        <v>90</v>
+      </c>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18">
+        <f t="shared" si="0"/>
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/Presupuestos.xlsx
+++ b/Presupuestos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9378B7-7D6B-4108-B579-078BC470C962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCBB515-6329-43A7-9D0C-CE2774088C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9481DF28-0B3E-48A4-9B25-BB3654989BFF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{9481DF28-0B3E-48A4-9B25-BB3654989BFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -356,6 +356,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -376,15 +385,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -748,22 +748,22 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="11" t="s">
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="12"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="14" t="s">
+      <c r="G1" s="15"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="15"/>
-      <c r="K1" s="16"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="19"/>
       <c r="L1" s="6" t="s">
         <v>6</v>
       </c>
@@ -1467,26 +1467,26 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="11">
         <v>2675</v>
       </c>
-      <c r="C2" s="18">
+      <c r="C2" s="11">
         <v>50</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="11">
         <v>20</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18" t="s">
+      <c r="E2" s="11"/>
+      <c r="F2" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="18">
+      <c r="G2" s="11">
         <v>70</v>
       </c>
-      <c r="H2" s="18">
+      <c r="H2" s="11">
         <f>B2-C2+D2-E2-G2</f>
         <v>2575</v>
       </c>
@@ -1511,260 +1511,260 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="11">
         <v>1000</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="11">
         <v>80</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="11">
         <v>140</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="11">
         <v>250</v>
       </c>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18">
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11">
         <f t="shared" si="0"/>
         <v>810</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="11">
         <v>2152</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="11">
         <v>60</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="11">
         <v>95</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="19" t="s">
+      <c r="E5" s="11"/>
+      <c r="F5" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="11">
         <v>33</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="11">
         <f t="shared" si="0"/>
         <v>2154</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="11">
         <v>164</v>
       </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18">
+      <c r="C6" s="11"/>
+      <c r="D6" s="11">
         <v>50</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18">
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11">
         <v>3</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="11">
         <f t="shared" si="0"/>
         <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="11">
         <v>2569</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18">
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11">
         <f t="shared" si="0"/>
         <v>2569</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="11">
         <v>194</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="11">
         <v>60</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18">
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11">
         <v>15</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="11">
         <f t="shared" si="0"/>
         <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="11">
         <v>440</v>
       </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18" t="s">
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18">
+      <c r="G9" s="11"/>
+      <c r="H9" s="11">
         <f t="shared" si="0"/>
         <v>440</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="11">
         <v>1920</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18">
+      <c r="C10" s="11"/>
+      <c r="D10" s="11">
         <v>215</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="11">
         <v>0</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="11">
         <v>14</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="11">
         <f t="shared" si="0"/>
         <v>2121</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="11">
         <v>759</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18">
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11">
         <f t="shared" si="0"/>
         <v>759</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="11">
         <v>300</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18">
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="11">
         <v>223</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18">
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11">
         <f t="shared" si="0"/>
         <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="11">
         <v>12</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="11">
         <v>45</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="11">
         <v>40</v>
       </c>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18">
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11">
         <v>18</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="11">
         <f t="shared" si="0"/>
         <v>-11</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="11">
         <v>280</v>
       </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18">
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11">
         <f t="shared" si="0"/>
         <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="11">
         <v>300</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9">
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
@@ -1787,45 +1787,45 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="11">
         <v>300</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="11">
         <v>75</v>
       </c>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18">
+      <c r="D18" s="11"/>
+      <c r="E18" s="11">
         <v>0</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="11">
         <v>88</v>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="11">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="11">
         <v>300</v>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="11">
         <v>90</v>
       </c>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18">
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11">
         <f t="shared" si="0"/>
         <v>210</v>
       </c>

--- a/Presupuestos.xlsx
+++ b/Presupuestos.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCBB515-6329-43A7-9D0C-CE2774088C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{9481DF28-0B3E-48A4-9B25-BB3654989BFF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9481DF28-0B3E-48A4-9B25-BB3654989BFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
